--- a/application_history_export.xlsx
+++ b/application_history_export.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
@@ -494,111 +494,91 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.961339+00:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:55:26.499559+00:00</t>
+          <t>2026-10-30T09:41:01.917770+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.915912+00:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:55:26.696138+00:00</t>
+          <t>2026-10-30T09:37:17.129959+00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,67 +588,87 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.716703+00:00</t>
+          <t>2026-10-30T09:36:36.191477+00:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:36:39.832904+00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.648338+00:00</t>
+          <t>2026-10-30T09:36:36.144956+00:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:36:39.731901+00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -678,92 +678,67 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.435350+00:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:55:22.450539+00:00</t>
+          <t>2026-10-30T09:36:35.944341+00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.587249+00:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:54:08.184651+00:00</t>
+          <t>2026-10-30T09:36:35.870659+00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -773,52 +748,57 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.528091+00:00</t>
+          <t>2026-10-30T09:36:35.627681+00:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:08.161794+00:00</t>
+          <t>2026-10-30T09:36:35.641278+00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.217183+00:00</t>
+          <t>2026-10-30T09:35:39.276487+00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -829,31 +809,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.098705+00:00</t>
+          <t>2026-10-30T09:34:33.230657+00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -864,7 +844,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -888,47 +868,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:02.651202+00:00</t>
+          <t>2026-10-30T09:33:50.037833+00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:02.667488+00:00</t>
+          <t>2026-10-30T09:33:53.705710+00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -938,12 +913,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.843310+00:00</t>
+          <t>2026-10-30T09:33:49.996004+00:00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:46.267923+00:00</t>
+          <t>2026-10-30T09:33:53.762785+00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -959,21 +934,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -983,52 +958,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.721086+00:00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:40:46.121141+00:00</t>
+          <t>2026-10-30T09:33:49.711734+00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.503127+00:00</t>
+          <t>2026-10-30T09:33:49.607779+00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1039,92 +1004,92 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.429006+00:00</t>
+          <t>2026-10-30T09:33:49.355224+00:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:33:49.359495+00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.206899+00:00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:40:41.213183+00:00</t>
+          <t>2026-10-30T09:31:48.218153+00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1148,12 +1113,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:27.230912+00:00</t>
+          <t>2026-10-30T09:29:56.789613+00:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:31.513378+00:00</t>
+          <t>2026-10-30T09:30:06.648191+00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1169,7 +1134,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1193,12 +1158,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:27.148676+00:00</t>
+          <t>2026-10-30T09:29:56.703660+00:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:31.555037+00:00</t>
+          <t>2026-10-30T09:30:06.530025+00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1214,7 +1179,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1238,7 +1203,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.991886+00:00</t>
+          <t>2026-10-30T09:29:56.512045+00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1249,7 +1214,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1273,7 +1238,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.941226+00:00</t>
+          <t>2026-10-30T09:29:56.445263+00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1284,7 +1249,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1308,12 +1273,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.741589+00:00</t>
+          <t>2026-10-30T09:29:56.246020+00:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.758542+00:00</t>
+          <t>2026-10-30T09:29:56.250270+00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1334,97 +1299,77 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:29.119850+00:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:28:32.850951+00:00</t>
+          <t>2026-10-30T09:29:21.889733+00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:29.011870+00:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:28:32.868519+00:00</t>
+          <t>2026-10-30T09:27:52.170654+00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1433,22 +1378,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Test Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://boards.greenhouse.io/demo/jobs/123</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.803528+00:00</t>
+          <t>2026-10-30T09:23:45.656690+00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1459,92 +1404,97 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>ThinkNovaa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>https://forms.gle/9HJpaunuknS7UUuq5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.757673+00:00</t>
+          <t>2026-10-30T08:01:35.837268+00:00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-30T08:01:40.333924+00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Needs manual action</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://in.linkedin.com/jobs/view/aws-data-engineer-at-tata-consultancy-services-4471266502?trk=public_jobs_topcard-title</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.594080+00:00</t>
+          <t>2026-10-30T08:01:21.198665+00:00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.598769+00:00</t>
+          <t>2026-10-30T08:01:25.453252+00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Needs manual action</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1568,12 +1518,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.956231+00:00</t>
+          <t>2026-10-30T07:17:45.794888+00:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:35.805917+00:00</t>
+          <t>2026-10-30T07:17:49.757864+00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1589,7 +1539,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1613,12 +1563,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.880538+00:00</t>
+          <t>2026-10-30T07:17:45.689817+00:00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:35.629247+00:00</t>
+          <t>2026-10-30T07:17:49.775544+00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1634,7 +1584,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1658,7 +1608,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.691933+00:00</t>
+          <t>2026-10-30T07:17:45.483698+00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1669,7 +1619,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1693,7 +1643,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.642178+00:00</t>
+          <t>2026-10-30T07:17:45.407175+00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1704,7 +1654,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1728,12 +1678,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.475217+00:00</t>
+          <t>2026-10-30T07:17:45.169303+00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.480037+00:00</t>
+          <t>2026-10-30T07:17:45.175198+00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1754,7 +1704,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1778,12 +1728,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:09.110128+00:00</t>
+          <t>2026-10-30T06:55:22.961339+00:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:12.734849+00:00</t>
+          <t>2026-10-30T06:55:26.499559+00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1799,7 +1749,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1823,12 +1773,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:09.002983+00:00</t>
+          <t>2026-10-30T06:55:22.915912+00:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:12.876683+00:00</t>
+          <t>2026-10-30T06:55:26.696138+00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1844,7 +1794,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1868,7 +1818,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.770351+00:00</t>
+          <t>2026-10-30T06:55:22.716703+00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1879,7 +1829,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1903,7 +1853,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.709671+00:00</t>
+          <t>2026-10-30T06:55:22.648338+00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1914,7 +1864,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1938,12 +1888,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.483162+00:00</t>
+          <t>2026-10-30T06:55:22.435350+00:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.496816+00:00</t>
+          <t>2026-10-30T06:55:22.450539+00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1964,7 +1914,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1988,12 +1938,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.721067+00:00</t>
+          <t>2026-10-30T06:54:03.587249+00:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:57.378218+00:00</t>
+          <t>2026-10-30T06:54:08.184651+00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2009,7 +1959,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2033,12 +1983,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.663662+00:00</t>
+          <t>2026-10-30T06:54:03.528091+00:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:57.301423+00:00</t>
+          <t>2026-10-30T06:54:08.161794+00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2054,7 +2004,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2078,7 +2028,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.476751+00:00</t>
+          <t>2026-10-30T06:54:03.217183+00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2089,7 +2039,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2113,7 +2063,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.398853+00:00</t>
+          <t>2026-10-30T06:54:03.098705+00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2124,7 +2074,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2148,12 +2098,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.179302+00:00</t>
+          <t>2026-10-30T06:54:02.651202+00:00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.187478+00:00</t>
+          <t>2026-10-30T06:54:02.667488+00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2174,7 +2124,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2198,12 +2148,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.758990+00:00</t>
+          <t>2026-10-30T06:40:41.843310+00:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:32.156605+00:00</t>
+          <t>2026-10-30T06:40:46.267923+00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2219,7 +2169,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2243,12 +2193,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.634676+00:00</t>
+          <t>2026-10-30T06:40:41.721086+00:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:32.128066+00:00</t>
+          <t>2026-10-30T06:40:46.121141+00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2264,7 +2214,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2288,7 +2238,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.406827+00:00</t>
+          <t>2026-10-30T06:40:41.503127+00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2299,7 +2249,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2323,7 +2273,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.340779+00:00</t>
+          <t>2026-10-30T06:40:41.429006+00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2334,7 +2284,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2358,12 +2308,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.117530+00:00</t>
+          <t>2026-10-30T06:40:41.206899+00:00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.121492+00:00</t>
+          <t>2026-10-30T06:40:41.213183+00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2384,7 +2334,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2408,12 +2358,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.930445+00:00</t>
+          <t>2026-10-30T06:30:27.230912+00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:27.479591+00:00</t>
+          <t>2026-10-30T06:30:31.513378+00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2429,7 +2379,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2453,12 +2403,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.842116+00:00</t>
+          <t>2026-10-30T06:30:27.148676+00:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:27.511243+00:00</t>
+          <t>2026-10-30T06:30:31.555037+00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2474,7 +2424,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2498,7 +2448,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.590670+00:00</t>
+          <t>2026-10-30T06:30:26.991886+00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2509,7 +2459,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2533,7 +2483,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.491389+00:00</t>
+          <t>2026-10-30T06:30:26.941226+00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2544,7 +2494,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2568,12 +2518,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.243568+00:00</t>
+          <t>2026-10-30T06:30:26.741589+00:00</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.251912+00:00</t>
+          <t>2026-10-30T06:30:26.758542+00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2594,21 +2544,21 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2618,67 +2568,87 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.392093+00:00</t>
+          <t>2026-10-30T06:28:29.119850+00:00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:28:32.850951+00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.314163+00:00</t>
+          <t>2026-10-30T06:28:29.011870+00:00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:28:32.868519+00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2688,93 +2658,67 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.106477+00:00</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-10-29T16:09:46.112454+00:00</t>
+          <t>2026-10-30T06:28:28.803528+00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.204055+00:00</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:31.225773+00:00</t>
+          <t>2026-10-30T06:28:28.757673+00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error during application: </t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2784,43 +2728,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.108936+00:00</t>
+          <t>2026-10-30T06:28:28.594080+00:00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.140158+00:00</t>
+          <t>2026-10-30T06:28:28.598769+00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error during application: </t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2830,67 +2778,87 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.736929+00:00</t>
+          <t>2026-10-30T05:33:31.956231+00:00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-10-30T05:33:35.805917+00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.641685+00:00</t>
+          <t>2026-10-30T05:33:31.880538+00:00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-10-30T05:33:35.629247+00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2900,92 +2868,67 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.320583+00:00</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:30.326118+00:00</t>
+          <t>2026-10-30T05:33:31.691933+00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:54.287293+00:00</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:42:58.032370+00:00</t>
+          <t>2026-10-30T05:33:31.642178+00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2995,28 +2938,33 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:54.177389+00:00</t>
+          <t>2026-10-30T05:33:31.475217+00:00</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:58.180926+00:00</t>
+          <t>2026-10-30T05:33:31.480037+00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3040,12 +2988,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:27.443320+00:00</t>
+          <t>2026-10-30T05:16:09.110128+00:00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:31.782682+00:00</t>
+          <t>2026-10-30T05:16:12.734849+00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3061,7 +3009,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3085,12 +3033,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:27.356218+00:00</t>
+          <t>2026-10-30T05:16:09.002983+00:00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:31.839164+00:00</t>
+          <t>2026-10-30T05:16:12.876683+00:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3106,7 +3054,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3130,7 +3078,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:22.075427+00:00</t>
+          <t>2026-10-30T05:16:08.770351+00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3141,7 +3089,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3165,7 +3113,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:22.021258+00:00</t>
+          <t>2026-10-30T05:16:08.709671+00:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3176,7 +3124,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3200,12 +3148,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:21.847719+00:00</t>
+          <t>2026-10-30T05:16:08.483162+00:00</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:21.862410+00:00</t>
+          <t>2026-10-30T05:16:08.496816+00:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3226,7 +3174,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3250,12 +3198,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:03.584167+00:00</t>
+          <t>2026-10-30T05:10:53.721067+00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:06.925683+00:00</t>
+          <t>2026-10-30T05:10:57.378218+00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3271,7 +3219,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3295,12 +3243,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:03.491808+00:00</t>
+          <t>2026-10-30T05:10:53.663662+00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:06.712055+00:00</t>
+          <t>2026-10-30T05:10:57.301423+00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3316,7 +3264,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3340,7 +3288,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.474877+00:00</t>
+          <t>2026-10-30T05:10:53.476751+00:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3351,7 +3299,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3375,7 +3323,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.425587+00:00</t>
+          <t>2026-10-30T05:10:53.398853+00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3386,7 +3334,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3410,12 +3358,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.260452+00:00</t>
+          <t>2026-10-30T05:10:53.179302+00:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.272949+00:00</t>
+          <t>2026-10-30T05:10:53.187478+00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3436,7 +3384,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3460,12 +3408,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:56.380448+00:00</t>
+          <t>2026-10-30T04:49:27.758990+00:00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-29T14:27:00.101381+00:00</t>
+          <t>2026-10-30T04:49:32.156605+00:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3481,7 +3429,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3505,12 +3453,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:56.297032+00:00</t>
+          <t>2026-10-30T04:49:27.634676+00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:59.916918+00:00</t>
+          <t>2026-10-30T04:49:32.128066+00:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3526,7 +3474,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3550,7 +3498,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.411181+00:00</t>
+          <t>2026-10-30T04:49:27.406827+00:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3561,7 +3509,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3585,7 +3533,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.360006+00:00</t>
+          <t>2026-10-30T04:49:27.340779+00:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3596,7 +3544,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3620,12 +3568,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.196399+00:00</t>
+          <t>2026-10-30T04:49:27.117530+00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.202839+00:00</t>
+          <t>2026-10-30T04:49:27.121492+00:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3646,7 +3594,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3670,12 +3618,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:32.778042+00:00</t>
+          <t>2026-10-29T16:16:22.930445+00:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:36.309759+00:00</t>
+          <t>2026-10-29T16:16:27.479591+00:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3691,7 +3639,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3715,12 +3663,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:32.702160+00:00</t>
+          <t>2026-10-29T16:16:22.842116+00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:36.201815+00:00</t>
+          <t>2026-10-29T16:16:27.511243+00:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3736,21 +3684,21 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3760,87 +3708,67 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:16.189456+00:00</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:12:19.790801+00:00</t>
+          <t>2026-10-29T16:16:22.590670+00:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:16.112025+00:00</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:12:19.994696+00:00</t>
+          <t>2026-10-29T16:16:22.491389+00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3850,42 +3778,57 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.875174+00:00</t>
+          <t>2026-10-29T16:16:22.243568+00:00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:16:22.251912+00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.820231+00:00</t>
+          <t>2026-10-29T16:09:46.392093+00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3896,57 +3839,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.636542+00:00</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:12:11.641061+00:00</t>
+          <t>2026-10-29T16:09:46.314163+00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3970,42 +3898,47 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:57.519802+00:00</t>
+          <t>2026-10-29T16:09:46.106477+00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-10-29T13:32:01.165745+00:00</t>
+          <t>2026-10-29T16:09:46.112454+00:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4015,42 +3948,43 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:57.442785+00:00</t>
+          <t>2026-10-29T15:57:31.204055+00:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-10-29T13:32:01.304468+00:00</t>
+          <t>2026-10-29T15:57:31.225773+00:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t xml:space="preserve">Error during application: </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4060,42 +3994,53 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.587292+00:00</t>
+          <t>2026-10-29T15:57:31.108936+00:00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:57:31.140158+00:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error during application: </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.538735+00:00</t>
+          <t>2026-10-29T15:57:30.736929+00:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4106,57 +4051,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.383044+00:00</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2026-10-29T13:31:52.386957+00:00</t>
+          <t>2026-10-29T15:57:30.641685+00:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4180,42 +4110,47 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:02.362074+00:00</t>
+          <t>2026-10-29T15:57:30.320583+00:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:08.021605+00:00</t>
+          <t>2026-10-29T15:57:30.326118+00:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4225,12 +4160,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:02.284388+00:00</t>
+          <t>2026-10-29T15:42:54.287293+00:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:08.052421+00:00</t>
+          <t>2026-10-29T15:42:58.032370+00:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4246,21 +4181,21 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4270,67 +4205,87 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.427420+00:00</t>
+          <t>2026-10-29T15:42:54.177389+00:00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:42:58.180926+00:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.330669+00:00</t>
+          <t>2026-10-29T14:38:27.443320+00:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:38:31.782682+00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4340,47 +4295,42 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.020667+00:00</t>
+          <t>2026-10-29T14:38:27.356218+00:00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.032548+00:00</t>
+          <t>2026-10-29T14:38:31.839164+00:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4390,87 +4340,67 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:43.958358+00:00</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026-10-29T12:35:47.842477+00:00</t>
+          <t>2026-10-29T14:38:22.075427+00:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:43.875277+00:00</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-10-29T12:35:47.826697+00:00</t>
+          <t>2026-10-29T14:38:22.021258+00:00</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4480,67 +4410,92 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.679674+00:00</t>
+          <t>2026-10-29T14:38:21.847719+00:00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:38:21.862410+00:00</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.612816+00:00</t>
+          <t>2026-10-29T14:33:03.584167+00:00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:33:06.925683+00:00</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4550,102 +4505,87 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.402785+00:00</t>
+          <t>2026-10-29T14:33:03.491808+00:00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.409018+00:00</t>
+          <t>2026-10-29T14:33:06.712055+00:00</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CredHive</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI Systems)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engineer-intern-at-credhive-4483104685?trk=public_jobs_topcard-title</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-29T07:40:04.055848+00:00</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-10-29T07:40:08.038425+00:00</t>
+          <t>2026-10-29T14:32:58.474877+00:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.906851+00:00</t>
+          <t>2026-10-29T14:32:58.425587+00:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4656,42 +4596,57 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.830142+00:00</t>
+          <t>2026-10-29T14:32:58.260452+00:00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:32:58.272949+00:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4715,47 +4670,42 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.609768+00:00</t>
+          <t>2026-10-29T14:26:56.380448+00:00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.623780+00:00</t>
+          <t>2026-10-29T14:27:00.101381+00:00</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4765,12 +4715,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:04.749633+00:00</t>
+          <t>2026-10-29T14:26:56.297032+00:00</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:08.318789+00:00</t>
+          <t>2026-10-29T14:26:59.916918+00:00</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4786,21 +4736,21 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4810,52 +4760,42 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:04.683354+00:00</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2026-10-29T07:35:08.243543+00:00</t>
+          <t>2026-10-29T14:26:51.411181+00:00</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:00.218486+00:00</t>
+          <t>2026-10-29T14:26:51.360006+00:00</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4866,84 +4806,1354 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:00.030655+00:00</t>
+          <t>2026-10-29T14:26:51.196399+00:00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:26:51.202839+00:00</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
+        <v>31</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:14:32.778042+00:00</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:14:36.309759+00:00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>30</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:14:32.702160+00:00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:14:36.201815+00:00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>29</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:16.189456+00:00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:19.790801+00:00</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>28</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:16.112025+00:00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:19.994696+00:00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>27</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:11.875174+00:00</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>26</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:11.820231+00:00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>25</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:11.636542+00:00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:11.641061+00:00</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>24</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:57.519802+00:00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:32:01.165745+00:00</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>23</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:57.442785+00:00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:32:01.304468+00:00</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>22</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:52.587292+00:00</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>21</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:52.538735+00:00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>20</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:52.383044+00:00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:31:52.386957+00:00</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>19</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:01:02.362074+00:00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:01:08.021605+00:00</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>18</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:01:02.284388+00:00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:01:08.052421+00:00</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>17</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:00:30.427420+00:00</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>16</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:00:30.330669+00:00</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>15</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:00:30.020667+00:00</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:00:30.032548+00:00</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>14</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:43.958358+00:00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:47.842477+00:00</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>13</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:43.875277+00:00</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:47.826697+00:00</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>12</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.679674+00:00</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>11</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.612816+00:00</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>10</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.402785+00:00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.409018+00:00</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>9</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CredHive</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (AI Systems)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-intern-at-credhive-4483104685?trk=public_jobs_topcard-title</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:40:04.055848+00:00</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:40:08.038425+00:00</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Needs manual action</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>8</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.906851+00:00</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>7</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.830142+00:00</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>6</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.609768+00:00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.623780+00:00</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:04.749633+00:00</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:08.318789+00:00</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:04.683354+00:00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:08.243543+00:00</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>3</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:24:00.218486+00:00</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:24:00.030655+00:00</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
         <v>1</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>smoke-001</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>TestCorp</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>http://localhost:5000/test_form.html</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>2026-10-29T07:23:59.720577+00:00</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>2026-10-29T07:23:59.730420+00:00</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>Submitted successfully</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>Confirmed in test</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>Smoke test OK</t>
         </is>

--- a/application_history_export.xlsx
+++ b/application_history_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:01.917770+00:00</t>
+          <t>2026-10-30T09:42:32.723232+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -529,56 +529,66 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-30T09:37:17.129959+00:00</t>
+          <t>2026-10-30T09:41:38.137822+00:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:41:43.388397+00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -588,12 +598,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:36.191477+00:00</t>
+          <t>2026-10-30T09:41:38.044903+00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:39.832904+00:00</t>
+          <t>2026-10-30T09:41:43.352137+00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -609,21 +619,21 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -633,52 +643,42 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:36.144956+00:00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:36:39.731901+00:00</t>
+          <t>2026-10-30T09:41:37.711858+00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.944341+00:00</t>
+          <t>2026-10-30T09:41:37.610015+00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -689,92 +689,92 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.870659+00:00</t>
+          <t>2026-10-30T09:41:37.198515+00:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:41:37.216911+00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.627681+00:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:36:35.641278+00:00</t>
+          <t>2026-10-30T09:41:01.917770+00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-30T09:35:39.276487+00:00</t>
+          <t>2026-10-30T09:37:17.129959+00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -809,56 +809,66 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-30T09:34:33.230657+00:00</t>
+          <t>2026-10-30T09:36:36.191477+00:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:36:39.832904+00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -868,12 +878,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:50.037833+00:00</t>
+          <t>2026-10-30T09:36:36.144956+00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:53.705710+00:00</t>
+          <t>2026-10-30T09:36:39.731901+00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -889,21 +899,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -913,52 +923,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.996004+00:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:33:53.762785+00:00</t>
+          <t>2026-10-30T09:36:35.944341+00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.711734+00:00</t>
+          <t>2026-10-30T09:36:35.870659+00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -969,92 +969,92 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.607779+00:00</t>
+          <t>2026-10-30T09:36:35.627681+00:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:36:35.641278+00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.355224+00:00</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:33:49.359495+00:00</t>
+          <t>2026-10-30T09:35:39.276487+00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-30T09:31:48.218153+00:00</t>
+          <t>2026-10-30T09:34:33.230657+00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1089,7 +1089,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.789613+00:00</t>
+          <t>2026-10-30T09:33:50.037833+00:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-30T09:30:06.648191+00:00</t>
+          <t>2026-10-30T09:33:53.705710+00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1134,7 +1134,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.703660+00:00</t>
+          <t>2026-10-30T09:33:49.996004+00:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-30T09:30:06.530025+00:00</t>
+          <t>2026-10-30T09:33:53.762785+00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1179,7 +1179,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.512045+00:00</t>
+          <t>2026-10-30T09:33:49.711734+00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.445263+00:00</t>
+          <t>2026-10-30T09:33:49.607779+00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1249,7 +1249,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.246020+00:00</t>
+          <t>2026-10-30T09:33:49.355224+00:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.250270+00:00</t>
+          <t>2026-10-30T09:33:49.359495+00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1299,7 +1299,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:21.889733+00:00</t>
+          <t>2026-10-30T09:31:48.218153+00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1334,167 +1334,167 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-30T09:27:52.170654+00:00</t>
+          <t>2026-10-30T09:29:56.789613+00:00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:30:06.648191+00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Test Company</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/demo/jobs/123</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-30T09:23:45.656690+00:00</t>
+          <t>2026-10-30T09:29:56.703660+00:00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:30:06.530025+00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ThinkNovaa</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://forms.gle/9HJpaunuknS7UUuq5</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30T08:01:35.837268+00:00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-10-30T08:01:40.333924+00:00</t>
+          <t>2026-10-30T09:29:56.512045+00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/aws-data-engineer-at-tata-consultancy-services-4471266502?trk=public_jobs_topcard-title</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-30T08:01:21.198665+00:00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-10-30T08:01:25.453252+00:00</t>
+          <t>2026-10-30T09:29:56.445263+00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1518,97 +1518,92 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.794888+00:00</t>
+          <t>2026-10-30T09:29:56.246020+00:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:49.757864+00:00</t>
+          <t>2026-10-30T09:29:56.250270+00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.689817+00:00</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-10-30T07:17:49.775544+00:00</t>
+          <t>2026-10-30T09:29:21.889733+00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.483698+00:00</t>
+          <t>2026-10-30T09:27:52.170654+00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1619,31 +1614,31 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Test Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>https://boards.greenhouse.io/demo/jobs/123</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.407175+00:00</t>
+          <t>2026-10-30T09:23:45.656690+00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1654,116 +1649,111 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>ThinkNovaa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://forms.gle/9HJpaunuknS7UUuq5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.169303+00:00</t>
+          <t>2026-10-30T08:01:35.837268+00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.175198+00:00</t>
+          <t>2026-10-30T08:01:40.333924+00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Needs manual action</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://in.linkedin.com/jobs/view/aws-data-engineer-at-tata-consultancy-services-4471266502?trk=public_jobs_topcard-title</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.961339+00:00</t>
+          <t>2026-10-30T08:01:21.198665+00:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:26.499559+00:00</t>
+          <t>2026-10-30T08:01:25.453252+00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Needs manual action</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1773,12 +1763,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.915912+00:00</t>
+          <t>2026-10-30T07:17:45.794888+00:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:26.696138+00:00</t>
+          <t>2026-10-30T07:17:49.757864+00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1794,21 +1784,21 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1818,42 +1808,52 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.716703+00:00</t>
+          <t>2026-10-30T07:17:45.689817+00:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-30T07:17:49.775544+00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.648338+00:00</t>
+          <t>2026-10-30T07:17:45.483698+00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1864,57 +1864,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.435350+00:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:55:22.450539+00:00</t>
+          <t>2026-10-30T07:17:45.407175+00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1938,42 +1923,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.587249+00:00</t>
+          <t>2026-10-30T07:17:45.169303+00:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:08.184651+00:00</t>
+          <t>2026-10-30T07:17:45.175198+00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1983,12 +1973,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.528091+00:00</t>
+          <t>2026-10-30T06:55:22.961339+00:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:08.161794+00:00</t>
+          <t>2026-10-30T06:55:26.499559+00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2004,21 +1994,21 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2028,42 +2018,52 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.217183+00:00</t>
+          <t>2026-10-30T06:55:22.915912+00:00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:55:26.696138+00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.098705+00:00</t>
+          <t>2026-10-30T06:55:22.716703+00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2074,57 +2074,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:02.651202+00:00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:54:02.667488+00:00</t>
+          <t>2026-10-30T06:55:22.648338+00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2148,42 +2133,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.843310+00:00</t>
+          <t>2026-10-30T06:55:22.435350+00:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:46.267923+00:00</t>
+          <t>2026-10-30T06:55:22.450539+00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2193,12 +2183,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.721086+00:00</t>
+          <t>2026-10-30T06:54:03.587249+00:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:46.121141+00:00</t>
+          <t>2026-10-30T06:54:08.184651+00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2214,21 +2204,21 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2238,42 +2228,52 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.503127+00:00</t>
+          <t>2026-10-30T06:54:03.528091+00:00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:54:08.161794+00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.429006+00:00</t>
+          <t>2026-10-30T06:54:03.217183+00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2284,57 +2284,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.206899+00:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:40:41.213183+00:00</t>
+          <t>2026-10-30T06:54:03.098705+00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2358,42 +2343,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:27.230912+00:00</t>
+          <t>2026-10-30T06:54:02.651202+00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:31.513378+00:00</t>
+          <t>2026-10-30T06:54:02.667488+00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2403,12 +2393,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:27.148676+00:00</t>
+          <t>2026-10-30T06:40:41.843310+00:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:31.555037+00:00</t>
+          <t>2026-10-30T06:40:46.267923+00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2424,21 +2414,21 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2448,42 +2438,52 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.991886+00:00</t>
+          <t>2026-10-30T06:40:41.721086+00:00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:40:46.121141+00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.941226+00:00</t>
+          <t>2026-10-30T06:40:41.503127+00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2494,57 +2494,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.741589+00:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:30:26.758542+00:00</t>
+          <t>2026-10-30T06:40:41.429006+00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2568,42 +2553,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:29.119850+00:00</t>
+          <t>2026-10-30T06:40:41.206899+00:00</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:32.850951+00:00</t>
+          <t>2026-10-30T06:40:41.213183+00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2613,12 +2603,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:29.011870+00:00</t>
+          <t>2026-10-30T06:30:27.230912+00:00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:32.868519+00:00</t>
+          <t>2026-10-30T06:30:31.513378+00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2634,21 +2624,21 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2658,42 +2648,52 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.803528+00:00</t>
+          <t>2026-10-30T06:30:27.148676+00:00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:30:31.555037+00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.757673+00:00</t>
+          <t>2026-10-30T06:30:26.991886+00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2704,57 +2704,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.594080+00:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:28:28.598769+00:00</t>
+          <t>2026-10-30T06:30:26.941226+00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2778,42 +2763,47 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.956231+00:00</t>
+          <t>2026-10-30T06:30:26.741589+00:00</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:35.805917+00:00</t>
+          <t>2026-10-30T06:30:26.758542+00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2823,12 +2813,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.880538+00:00</t>
+          <t>2026-10-30T06:28:29.119850+00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:35.629247+00:00</t>
+          <t>2026-10-30T06:28:32.850951+00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2844,21 +2834,21 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2868,42 +2858,52 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.691933+00:00</t>
+          <t>2026-10-30T06:28:29.011870+00:00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-10-30T06:28:32.868519+00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.642178+00:00</t>
+          <t>2026-10-30T06:28:28.803528+00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2914,57 +2914,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.475217+00:00</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-10-30T05:33:31.480037+00:00</t>
+          <t>2026-10-30T06:28:28.757673+00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2988,42 +2973,47 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:09.110128+00:00</t>
+          <t>2026-10-30T06:28:28.594080+00:00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:12.734849+00:00</t>
+          <t>2026-10-30T06:28:28.598769+00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3033,12 +3023,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:09.002983+00:00</t>
+          <t>2026-10-30T05:33:31.956231+00:00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:12.876683+00:00</t>
+          <t>2026-10-30T05:33:35.805917+00:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3054,21 +3044,21 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3078,42 +3068,52 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.770351+00:00</t>
+          <t>2026-10-30T05:33:31.880538+00:00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-10-30T05:33:35.629247+00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.709671+00:00</t>
+          <t>2026-10-30T05:33:31.691933+00:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3124,57 +3124,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.483162+00:00</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-10-30T05:16:08.496816+00:00</t>
+          <t>2026-10-30T05:33:31.642178+00:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3198,42 +3183,47 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.721067+00:00</t>
+          <t>2026-10-30T05:33:31.475217+00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:57.378218+00:00</t>
+          <t>2026-10-30T05:33:31.480037+00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3243,12 +3233,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.663662+00:00</t>
+          <t>2026-10-30T05:16:09.110128+00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:57.301423+00:00</t>
+          <t>2026-10-30T05:16:12.734849+00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3264,21 +3254,21 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3288,42 +3278,52 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.476751+00:00</t>
+          <t>2026-10-30T05:16:09.002983+00:00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-30T05:16:12.876683+00:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.398853+00:00</t>
+          <t>2026-10-30T05:16:08.770351+00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3334,57 +3334,42 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.179302+00:00</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2026-10-30T05:10:53.187478+00:00</t>
+          <t>2026-10-30T05:16:08.709671+00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3408,42 +3393,47 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.758990+00:00</t>
+          <t>2026-10-30T05:16:08.483162+00:00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:32.156605+00:00</t>
+          <t>2026-10-30T05:16:08.496816+00:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3453,12 +3443,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.634676+00:00</t>
+          <t>2026-10-30T05:10:53.721067+00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:32.128066+00:00</t>
+          <t>2026-10-30T05:10:57.378218+00:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3474,21 +3464,21 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3498,42 +3488,52 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.406827+00:00</t>
+          <t>2026-10-30T05:10:53.663662+00:00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-10-30T05:10:57.301423+00:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.340779+00:00</t>
+          <t>2026-10-30T05:10:53.476751+00:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3544,57 +3544,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.117530+00:00</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-10-30T04:49:27.121492+00:00</t>
+          <t>2026-10-30T05:10:53.398853+00:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3618,42 +3603,47 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.930445+00:00</t>
+          <t>2026-10-30T05:10:53.179302+00:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:27.479591+00:00</t>
+          <t>2026-10-30T05:10:53.187478+00:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3663,12 +3653,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.842116+00:00</t>
+          <t>2026-10-30T04:49:27.758990+00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:27.511243+00:00</t>
+          <t>2026-10-30T04:49:32.156605+00:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3684,21 +3674,21 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3708,42 +3698,52 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.590670+00:00</t>
+          <t>2026-10-30T04:49:27.634676+00:00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-10-30T04:49:32.128066+00:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.491389+00:00</t>
+          <t>2026-10-30T04:49:27.406827+00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3754,71 +3754,56 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.243568+00:00</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2026-10-29T16:16:22.251912+00:00</t>
+          <t>2026-10-30T04:49:27.340779+00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3828,67 +3813,92 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.392093+00:00</t>
+          <t>2026-10-30T04:49:27.117530+00:00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-10-30T04:49:27.121492+00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.314163+00:00</t>
+          <t>2026-10-29T16:16:22.930445+00:00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:16:27.479591+00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3898,47 +3908,42 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.106477+00:00</t>
+          <t>2026-10-29T16:16:22.842116+00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.112454+00:00</t>
+          <t>2026-10-29T16:16:27.511243+00:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3948,89 +3953,67 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.204055+00:00</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:31.225773+00:00</t>
+          <t>2026-10-29T16:16:22.590670+00:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error during application: </t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.108936+00:00</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:31.140158+00:00</t>
+          <t>2026-10-29T16:16:22.491389+00:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error during application: </t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4040,42 +4023,57 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.736929+00:00</t>
+          <t>2026-10-29T16:16:22.243568+00:00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:16:22.251912+00:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.641685+00:00</t>
+          <t>2026-10-29T16:09:46.392093+00:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4086,57 +4084,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.320583+00:00</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:30.326118+00:00</t>
+          <t>2026-10-29T16:09:46.314163+00:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4160,42 +4143,47 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:54.287293+00:00</t>
+          <t>2026-10-29T16:09:46.106477+00:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:58.032370+00:00</t>
+          <t>2026-10-29T16:09:46.112454+00:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4205,42 +4193,43 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:54.177389+00:00</t>
+          <t>2026-10-29T15:57:31.204055+00:00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:58.180926+00:00</t>
+          <t>2026-10-29T15:57:31.225773+00:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t xml:space="preserve">Error during application: </t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4250,42 +4239,43 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:27.443320+00:00</t>
+          <t>2026-10-29T15:57:31.108936+00:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:31.782682+00:00</t>
+          <t>2026-10-29T15:57:31.140158+00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t xml:space="preserve">Error during application: </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4295,52 +4285,42 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:27.356218+00:00</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:38:31.839164+00:00</t>
+          <t>2026-10-29T15:57:30.736929+00:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:22.075427+00:00</t>
+          <t>2026-10-29T15:57:30.641685+00:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4351,42 +4331,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:22.021258+00:00</t>
+          <t>2026-10-29T15:57:30.320583+00:00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:57:30.326118+00:00</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4410,47 +4405,42 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:21.847719+00:00</t>
+          <t>2026-10-29T15:42:54.287293+00:00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:21.862410+00:00</t>
+          <t>2026-10-29T15:42:58.032370+00:00</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4460,12 +4450,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:03.584167+00:00</t>
+          <t>2026-10-29T15:42:54.177389+00:00</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:06.925683+00:00</t>
+          <t>2026-10-29T15:42:58.180926+00:00</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4481,21 +4471,21 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4505,12 +4495,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:03.491808+00:00</t>
+          <t>2026-10-29T14:38:27.443320+00:00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:06.712055+00:00</t>
+          <t>2026-10-29T14:38:31.782682+00:00</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4526,21 +4516,21 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4550,42 +4540,52 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.474877+00:00</t>
+          <t>2026-10-29T14:38:27.356218+00:00</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:38:31.839164+00:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.425587+00:00</t>
+          <t>2026-10-29T14:38:22.075427+00:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4596,57 +4596,42 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.260452+00:00</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:32:58.272949+00:00</t>
+          <t>2026-10-29T14:38:22.021258+00:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4670,42 +4655,47 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:56.380448+00:00</t>
+          <t>2026-10-29T14:38:21.847719+00:00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-10-29T14:27:00.101381+00:00</t>
+          <t>2026-10-29T14:38:21.862410+00:00</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4715,12 +4705,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:56.297032+00:00</t>
+          <t>2026-10-29T14:33:03.584167+00:00</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:59.916918+00:00</t>
+          <t>2026-10-29T14:33:06.925683+00:00</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4736,21 +4726,21 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4760,42 +4750,52 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.411181+00:00</t>
+          <t>2026-10-29T14:33:03.491808+00:00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:33:06.712055+00:00</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.360006+00:00</t>
+          <t>2026-10-29T14:32:58.474877+00:00</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4806,57 +4806,42 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.196399+00:00</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:26:51.202839+00:00</t>
+          <t>2026-10-29T14:32:58.425587+00:00</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4880,42 +4865,47 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:32.778042+00:00</t>
+          <t>2026-10-29T14:32:58.260452+00:00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:36.309759+00:00</t>
+          <t>2026-10-29T14:32:58.272949+00:00</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4925,12 +4915,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:32.702160+00:00</t>
+          <t>2026-10-29T14:26:56.380448+00:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:36.201815+00:00</t>
+          <t>2026-10-29T14:27:00.101381+00:00</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4946,21 +4936,21 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4970,12 +4960,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:16.189456+00:00</t>
+          <t>2026-10-29T14:26:56.297032+00:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:19.790801+00:00</t>
+          <t>2026-10-29T14:26:59.916918+00:00</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4991,21 +4981,21 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5015,52 +5005,42 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:16.112025+00:00</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:12:19.994696+00:00</t>
+          <t>2026-10-29T14:26:51.411181+00:00</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.875174+00:00</t>
+          <t>2026-10-29T14:26:51.360006+00:00</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5071,42 +5051,57 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.820231+00:00</t>
+          <t>2026-10-29T14:26:51.196399+00:00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:26:51.202839+00:00</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -5130,47 +5125,42 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.636542+00:00</t>
+          <t>2026-10-29T14:14:32.778042+00:00</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.641061+00:00</t>
+          <t>2026-10-29T14:14:36.309759+00:00</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5180,12 +5170,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:57.519802+00:00</t>
+          <t>2026-10-29T14:14:32.702160+00:00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-10-29T13:32:01.165745+00:00</t>
+          <t>2026-10-29T14:14:36.201815+00:00</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5201,21 +5191,21 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5225,12 +5215,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:57.442785+00:00</t>
+          <t>2026-10-29T14:12:16.189456+00:00</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-10-29T13:32:01.304468+00:00</t>
+          <t>2026-10-29T14:12:19.790801+00:00</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5246,21 +5236,21 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5270,42 +5260,52 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.587292+00:00</t>
+          <t>2026-10-29T14:12:16.112025+00:00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:12:19.994696+00:00</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.538735+00:00</t>
+          <t>2026-10-29T14:12:11.875174+00:00</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5316,57 +5316,42 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.383044+00:00</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2026-10-29T13:31:52.386957+00:00</t>
+          <t>2026-10-29T14:12:11.820231+00:00</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -5390,42 +5375,47 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:02.362074+00:00</t>
+          <t>2026-10-29T14:12:11.636542+00:00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:08.021605+00:00</t>
+          <t>2026-10-29T14:12:11.641061+00:00</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5435,12 +5425,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:02.284388+00:00</t>
+          <t>2026-10-29T13:31:57.519802+00:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:08.052421+00:00</t>
+          <t>2026-10-29T13:32:01.165745+00:00</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5456,21 +5446,21 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5480,42 +5470,52 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.427420+00:00</t>
+          <t>2026-10-29T13:31:57.442785+00:00</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:32:01.304468+00:00</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.330669+00:00</t>
+          <t>2026-10-29T13:31:52.587292+00:00</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5526,57 +5526,42 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.020667+00:00</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2026-10-29T13:00:30.032548+00:00</t>
+          <t>2026-10-29T13:31:52.538735+00:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5600,42 +5585,47 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:43.958358+00:00</t>
+          <t>2026-10-29T13:31:52.383044+00:00</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:47.842477+00:00</t>
+          <t>2026-10-29T13:31:52.386957+00:00</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5645,12 +5635,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:43.875277+00:00</t>
+          <t>2026-10-29T13:01:02.362074+00:00</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:47.826697+00:00</t>
+          <t>2026-10-29T13:01:08.021605+00:00</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5666,21 +5656,21 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5690,42 +5680,52 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.679674+00:00</t>
+          <t>2026-10-29T13:01:02.284388+00:00</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:01:08.052421+00:00</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.612816+00:00</t>
+          <t>2026-10-29T13:00:30.427420+00:00</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5736,116 +5736,106 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.402785+00:00</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>2026-10-29T12:35:38.409018+00:00</t>
+          <t>2026-10-29T13:00:30.330669+00:00</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CredHive</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI Systems)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engineer-intern-at-credhive-4483104685?trk=public_jobs_topcard-title</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10-29T07:40:04.055848+00:00</t>
+          <t>2026-10-29T13:00:30.020667+00:00</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-10-29T07:40:08.038425+00:00</t>
+          <t>2026-10-29T13:00:30.032548+00:00</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5855,67 +5845,87 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.906851+00:00</t>
+          <t>2026-10-29T12:35:43.958358+00:00</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:47.842477+00:00</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.830142+00:00</t>
+          <t>2026-10-29T12:35:43.875277+00:00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:47.826697+00:00</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5925,92 +5935,67 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.609768+00:00</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>2026-10-29T07:35:46.623780+00:00</t>
+          <t>2026-10-29T12:35:38.679674+00:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:04.749633+00:00</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>2026-10-29T07:35:08.318789+00:00</t>
+          <t>2026-10-29T12:35:38.612816+00:00</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6020,87 +6005,102 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:04.683354+00:00</t>
+          <t>2026-10-29T12:35:38.402785+00:00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:08.243543+00:00</t>
+          <t>2026-10-29T12:35:38.409018+00:00</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>CredHive</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Software Engineer Intern (AI Systems)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-intern-at-credhive-4483104685?trk=public_jobs_topcard-title</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:00.218486+00:00</t>
+          <t>2026-10-29T07:40:04.055848+00:00</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:40:08.038425+00:00</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Needs manual action</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:00.030655+00:00</t>
+          <t>2026-10-29T07:35:46.906851+00:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6111,49 +6111,294 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
+        <v>7</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.830142+00:00</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>6</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.609768+00:00</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.623780+00:00</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:04.749633+00:00</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:08.318789+00:00</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:04.683354+00:00</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:08.243543+00:00</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>3</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:24:00.218486+00:00</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:24:00.030655+00:00</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
         <v>1</v>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>smoke-001</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>TestCorp</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>http://localhost:5000/test_form.html</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>2026-10-29T07:23:59.720577+00:00</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>2026-10-29T07:23:59.730420+00:00</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>Submitted successfully</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>Confirmed in test</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>Smoke test OK</t>
         </is>

--- a/application_history_export.xlsx
+++ b/application_history_export.xlsx
@@ -413,18 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
@@ -494,56 +494,71 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>test-full-auto-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>AutoApply TestCorp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://127.0.0.1:5000/test_form.html</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-30T09:42:32.723232+00:00</t>
+          <t>2026-10-30T16:26:06.762460+00:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-30T16:26:10.897700+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Submitted at 2026-10-30T16:26:10.897681+00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ Application submitted successfully to AutoApply TestCorp!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>TestCo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,132 +568,132 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:38.137822+00:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:41:43.388397+00:00</t>
+          <t>2026-10-30T16:26:06.746108+00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>GoodSpace AI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Machine Learning Engineer Intern</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://www.naukri.com/job-listings-machine-learning-engineer-intern-goodspace-ai-noida-0-to-1-years-28102600219</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:38.044903+00:00</t>
+          <t>2026-10-30T16:19:12.069369+00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:43.352137+00:00</t>
+          <t>2026-10-30T16:19:15.474831+00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Needs manual action</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>MediNex Workforce</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Python Developer Intern</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://medinexworkforce.in/careers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:37.711858+00:00</t>
+          <t>2026-10-30T16:17:54.929903+00:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-30T16:18:02.409507+00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Needs manual action</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:37.610015+00:00</t>
+          <t>2026-10-30T11:36:03.964827+00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -689,7 +704,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -713,92 +728,97 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:37.198515+00:00</t>
+          <t>2026-10-30T11:35:08.123238+00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:37.216911+00:00</t>
+          <t>2026-10-30T11:35:13.257083+00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-30T09:41:01.917770+00:00</t>
+          <t>2026-10-30T11:35:07.982445+00:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:35:13.203889+00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-30T09:37:17.129959+00:00</t>
+          <t>2026-10-30T11:35:07.642154+00:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -809,66 +829,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:36.191477+00:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:36:39.832904+00:00</t>
+          <t>2026-10-30T11:35:07.552460+00:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -878,52 +888,57 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:36.144956+00:00</t>
+          <t>2026-10-30T11:35:07.264022+00:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:39.731901+00:00</t>
+          <t>2026-10-30T11:35:07.281363+00:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.944341+00:00</t>
+          <t>2026-10-30T09:42:32.723232+00:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -934,56 +949,66 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.870659+00:00</t>
+          <t>2026-10-30T09:41:38.137822+00:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:41:43.388397+00:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,57 +1018,52 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.627681+00:00</t>
+          <t>2026-10-30T09:41:38.044903+00:00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-30T09:36:35.641278+00:00</t>
+          <t>2026-10-30T09:41:43.352137+00:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-30T09:35:39.276487+00:00</t>
+          <t>2026-10-30T09:41:37.711858+00:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1054,31 +1074,31 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-30T09:34:33.230657+00:00</t>
+          <t>2026-10-30T09:41:37.610015+00:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1089,7 +1109,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1113,97 +1133,92 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:50.037833+00:00</t>
+          <t>2026-10-30T09:41:37.198515+00:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:53.705710+00:00</t>
+          <t>2026-10-30T09:41:37.216911+00:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.996004+00:00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:33:53.762785+00:00</t>
+          <t>2026-10-30T09:41:01.917770+00:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.711734+00:00</t>
+          <t>2026-10-30T09:37:17.129959+00:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1214,56 +1229,66 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.607779+00:00</t>
+          <t>2026-10-30T09:36:36.191477+00:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:36:39.832904+00:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1273,57 +1298,52 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.355224+00:00</t>
+          <t>2026-10-30T09:36:36.144956+00:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-30T09:33:49.359495+00:00</t>
+          <t>2026-10-30T09:36:39.731901+00:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-30T09:31:48.218153+00:00</t>
+          <t>2026-10-30T09:36:35.944341+00:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1334,66 +1354,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.789613+00:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-10-30T09:30:06.648191+00:00</t>
+          <t>2026-10-30T09:36:35.870659+00:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1403,52 +1413,57 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.703660+00:00</t>
+          <t>2026-10-30T09:36:35.627681+00:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-30T09:30:06.530025+00:00</t>
+          <t>2026-10-30T09:36:35.641278+00:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.512045+00:00</t>
+          <t>2026-10-30T09:35:39.276487+00:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1459,31 +1474,31 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.445263+00:00</t>
+          <t>2026-10-30T09:34:33.230657+00:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1494,7 +1509,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1518,92 +1533,97 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.246020+00:00</t>
+          <t>2026-10-30T09:33:50.037833+00:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:56.250270+00:00</t>
+          <t>2026-10-30T09:33:53.705710+00:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-30T09:29:21.889733+00:00</t>
+          <t>2026-10-30T09:33:49.996004+00:00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-30T09:33:53.762785+00:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>test_ats_1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashby Tech</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/demo/apply</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30T09:27:52.170654+00:00</t>
+          <t>2026-10-30T09:33:49.711734+00:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1614,31 +1634,31 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Test Company</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/demo/jobs/123</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-30T09:23:45.656690+00:00</t>
+          <t>2026-10-30T09:33:49.607779+00:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1649,97 +1669,92 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ThinkNovaa</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://forms.gle/9HJpaunuknS7UUuq5</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-30T08:01:35.837268+00:00</t>
+          <t>2026-10-30T09:33:49.355224+00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-30T08:01:40.333924+00:00</t>
+          <t>2026-10-30T09:33:49.359495+00:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/aws-data-engineer-at-tata-consultancy-services-4471266502?trk=public_jobs_topcard-title</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-30T08:01:21.198665+00:00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-10-30T08:01:25.453252+00:00</t>
+          <t>2026-10-30T09:31:48.218153+00:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1763,12 +1778,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.794888+00:00</t>
+          <t>2026-10-30T09:29:56.789613+00:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:49.757864+00:00</t>
+          <t>2026-10-30T09:30:06.648191+00:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1784,7 +1799,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1808,12 +1823,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.689817+00:00</t>
+          <t>2026-10-30T09:29:56.703660+00:00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:49.775544+00:00</t>
+          <t>2026-10-30T09:30:06.530025+00:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1829,7 +1844,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1853,7 +1868,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.483698+00:00</t>
+          <t>2026-10-30T09:29:56.512045+00:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1864,7 +1879,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1888,7 +1903,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.407175+00:00</t>
+          <t>2026-10-30T09:29:56.445263+00:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1899,7 +1914,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1923,12 +1938,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.169303+00:00</t>
+          <t>2026-10-30T09:29:56.246020+00:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-30T07:17:45.175198+00:00</t>
+          <t>2026-10-30T09:29:56.250270+00:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1949,97 +1964,77 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.961339+00:00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:55:26.499559+00:00</t>
+          <t>2026-10-30T09:29:21.889733+00:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>test_ats_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>Ashby Tech</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://jobs.ashbyhq.com/demo/apply</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.915912+00:00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-10-30T06:55:26.696138+00:00</t>
+          <t>2026-10-30T09:27:52.170654+00:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2048,22 +2043,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Test Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://boards.greenhouse.io/demo/jobs/123</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.716703+00:00</t>
+          <t>2026-10-30T09:23:45.656690+00:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2074,92 +2069,97 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>ThinkNovaa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>https://forms.gle/9HJpaunuknS7UUuq5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.648338+00:00</t>
+          <t>2026-10-30T08:01:35.837268+00:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-30T08:01:40.333924+00:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Needs manual action</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>https://in.linkedin.com/jobs/view/aws-data-engineer-at-tata-consultancy-services-4471266502?trk=public_jobs_topcard-title</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.435350+00:00</t>
+          <t>2026-10-30T08:01:21.198665+00:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-30T06:55:22.450539+00:00</t>
+          <t>2026-10-30T08:01:25.453252+00:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Needs manual action</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.587249+00:00</t>
+          <t>2026-10-30T07:17:45.794888+00:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:08.184651+00:00</t>
+          <t>2026-10-30T07:17:49.757864+00:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2204,7 +2204,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.528091+00:00</t>
+          <t>2026-10-30T07:17:45.689817+00:00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:08.161794+00:00</t>
+          <t>2026-10-30T07:17:49.775544+00:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2249,7 +2249,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.217183+00:00</t>
+          <t>2026-10-30T07:17:45.483698+00:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:03.098705+00:00</t>
+          <t>2026-10-30T07:17:45.407175+00:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2319,7 +2319,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:02.651202+00:00</t>
+          <t>2026-10-30T07:17:45.169303+00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-30T06:54:02.667488+00:00</t>
+          <t>2026-10-30T07:17:45.175198+00:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2369,7 +2369,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.843310+00:00</t>
+          <t>2026-10-30T06:55:22.961339+00:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:46.267923+00:00</t>
+          <t>2026-10-30T06:55:26.499559+00:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2414,7 +2414,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.721086+00:00</t>
+          <t>2026-10-30T06:55:22.915912+00:00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:46.121141+00:00</t>
+          <t>2026-10-30T06:55:26.696138+00:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2459,7 +2459,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.503127+00:00</t>
+          <t>2026-10-30T06:55:22.716703+00:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.429006+00:00</t>
+          <t>2026-10-30T06:55:22.648338+00:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2529,7 +2529,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.206899+00:00</t>
+          <t>2026-10-30T06:55:22.435350+00:00</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-30T06:40:41.213183+00:00</t>
+          <t>2026-10-30T06:55:22.450539+00:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:27.230912+00:00</t>
+          <t>2026-10-30T06:54:03.587249+00:00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:31.513378+00:00</t>
+          <t>2026-10-30T06:54:08.184651+00:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2624,7 +2624,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:27.148676+00:00</t>
+          <t>2026-10-30T06:54:03.528091+00:00</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:31.555037+00:00</t>
+          <t>2026-10-30T06:54:08.161794+00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2669,7 +2669,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.991886+00:00</t>
+          <t>2026-10-30T06:54:03.217183+00:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2704,7 +2704,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.941226+00:00</t>
+          <t>2026-10-30T06:54:03.098705+00:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2739,7 +2739,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.741589+00:00</t>
+          <t>2026-10-30T06:54:02.651202+00:00</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-30T06:30:26.758542+00:00</t>
+          <t>2026-10-30T06:54:02.667488+00:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2789,7 +2789,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:29.119850+00:00</t>
+          <t>2026-10-30T06:40:41.843310+00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:32.850951+00:00</t>
+          <t>2026-10-30T06:40:46.267923+00:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2834,7 +2834,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:29.011870+00:00</t>
+          <t>2026-10-30T06:40:41.721086+00:00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:32.868519+00:00</t>
+          <t>2026-10-30T06:40:46.121141+00:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2879,7 +2879,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.803528+00:00</t>
+          <t>2026-10-30T06:40:41.503127+00:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2914,7 +2914,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.757673+00:00</t>
+          <t>2026-10-30T06:40:41.429006+00:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2949,7 +2949,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.594080+00:00</t>
+          <t>2026-10-30T06:40:41.206899+00:00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:28.598769+00:00</t>
+          <t>2026-10-30T06:40:41.213183+00:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2999,7 +2999,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.956231+00:00</t>
+          <t>2026-10-30T06:30:27.230912+00:00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:35.805917+00:00</t>
+          <t>2026-10-30T06:30:31.513378+00:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.880538+00:00</t>
+          <t>2026-10-30T06:30:27.148676+00:00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:35.629247+00:00</t>
+          <t>2026-10-30T06:30:31.555037+00:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3089,7 +3089,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.691933+00:00</t>
+          <t>2026-10-30T06:30:26.991886+00:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3124,7 +3124,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.642178+00:00</t>
+          <t>2026-10-30T06:30:26.941226+00:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3159,7 +3159,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.475217+00:00</t>
+          <t>2026-10-30T06:30:26.741589+00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-30T05:33:31.480037+00:00</t>
+          <t>2026-10-30T06:30:26.758542+00:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3209,7 +3209,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:09.110128+00:00</t>
+          <t>2026-10-30T06:28:29.119850+00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:12.734849+00:00</t>
+          <t>2026-10-30T06:28:32.850951+00:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3254,7 +3254,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:09.002983+00:00</t>
+          <t>2026-10-30T06:28:29.011870+00:00</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:12.876683+00:00</t>
+          <t>2026-10-30T06:28:32.868519+00:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3299,7 +3299,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.770351+00:00</t>
+          <t>2026-10-30T06:28:28.803528+00:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3334,7 +3334,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.709671+00:00</t>
+          <t>2026-10-30T06:28:28.757673+00:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3369,7 +3369,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.483162+00:00</t>
+          <t>2026-10-30T06:28:28.594080+00:00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:08.496816+00:00</t>
+          <t>2026-10-30T06:28:28.598769+00:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3419,7 +3419,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.721067+00:00</t>
+          <t>2026-10-30T05:33:31.956231+00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:57.378218+00:00</t>
+          <t>2026-10-30T05:33:35.805917+00:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3464,7 +3464,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.663662+00:00</t>
+          <t>2026-10-30T05:33:31.880538+00:00</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:57.301423+00:00</t>
+          <t>2026-10-30T05:33:35.629247+00:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.476751+00:00</t>
+          <t>2026-10-30T05:33:31.691933+00:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3544,7 +3544,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.398853+00:00</t>
+          <t>2026-10-30T05:33:31.642178+00:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3579,7 +3579,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3603,12 +3603,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.179302+00:00</t>
+          <t>2026-10-30T05:33:31.475217+00:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-30T05:10:53.187478+00:00</t>
+          <t>2026-10-30T05:33:31.480037+00:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3629,7 +3629,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.758990+00:00</t>
+          <t>2026-10-30T05:16:09.110128+00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:32.156605+00:00</t>
+          <t>2026-10-30T05:16:12.734849+00:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3674,7 +3674,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.634676+00:00</t>
+          <t>2026-10-30T05:16:09.002983+00:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:32.128066+00:00</t>
+          <t>2026-10-30T05:16:12.876683+00:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.406827+00:00</t>
+          <t>2026-10-30T05:16:08.770351+00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3754,7 +3754,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.340779+00:00</t>
+          <t>2026-10-30T05:16:08.709671+00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3789,7 +3789,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.117530+00:00</t>
+          <t>2026-10-30T05:16:08.483162+00:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-10-30T04:49:27.121492+00:00</t>
+          <t>2026-10-30T05:16:08.496816+00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3839,7 +3839,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.930445+00:00</t>
+          <t>2026-10-30T05:10:53.721067+00:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:27.479591+00:00</t>
+          <t>2026-10-30T05:10:57.378218+00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3884,7 +3884,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.842116+00:00</t>
+          <t>2026-10-30T05:10:53.663662+00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:27.511243+00:00</t>
+          <t>2026-10-30T05:10:57.301423+00:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3929,7 +3929,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.590670+00:00</t>
+          <t>2026-10-30T05:10:53.476751+00:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3964,7 +3964,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.491389+00:00</t>
+          <t>2026-10-30T05:10:53.398853+00:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3999,7 +3999,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.243568+00:00</t>
+          <t>2026-10-30T05:10:53.179302+00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-10-29T16:16:22.251912+00:00</t>
+          <t>2026-10-30T05:10:53.187478+00:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4049,21 +4049,21 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4073,67 +4073,87 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.392093+00:00</t>
+          <t>2026-10-30T04:49:27.758990+00:00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-10-30T04:49:32.156605+00:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.314163+00:00</t>
+          <t>2026-10-30T04:49:27.634676+00:00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-10-30T04:49:32.128066+00:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4143,93 +4163,67 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-29T16:09:46.106477+00:00</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2026-10-29T16:09:46.112454+00:00</t>
+          <t>2026-10-30T04:49:27.406827+00:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.204055+00:00</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:31.225773+00:00</t>
+          <t>2026-10-30T04:49:27.340779+00:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error during application: </t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4239,43 +4233,47 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.108936+00:00</t>
+          <t>2026-10-30T04:49:27.117530+00:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:31.140158+00:00</t>
+          <t>2026-10-30T04:49:27.121492+00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error during application: </t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4285,67 +4283,87 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.736929+00:00</t>
+          <t>2026-10-29T16:16:22.930445+00:00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:16:27.479591+00:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.641685+00:00</t>
+          <t>2026-10-29T16:16:22.842116+00:00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:16:27.511243+00:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4355,92 +4373,67 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-29T15:57:30.320583+00:00</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:57:30.326118+00:00</t>
+          <t>2026-10-29T16:16:22.590670+00:00</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:54.287293+00:00</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026-10-29T15:42:58.032370+00:00</t>
+          <t>2026-10-29T16:16:22.491389+00:00</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4450,42 +4443,47 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:54.177389+00:00</t>
+          <t>2026-10-29T16:16:22.243568+00:00</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-10-29T15:42:58.180926+00:00</t>
+          <t>2026-10-29T16:16:22.251912+00:00</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4495,87 +4493,67 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:27.443320+00:00</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:38:31.782682+00:00</t>
+          <t>2026-10-29T16:09:46.392093+00:00</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:27.356218+00:00</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:38:31.839164+00:00</t>
+          <t>2026-10-29T16:09:46.314163+00:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4585,67 +4563,93 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:22.075427+00:00</t>
+          <t>2026-10-29T16:09:46.106477+00:00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:09:46.112454+00:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:22.021258+00:00</t>
+          <t>2026-10-29T15:57:31.204055+00:00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:57:31.225773+00:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error during application: </t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4655,47 +4659,43 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:21.847719+00:00</t>
+          <t>2026-10-29T15:57:31.108936+00:00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-10-29T14:38:21.862410+00:00</t>
+          <t>2026-10-29T15:57:31.140158+00:00</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t xml:space="preserve">Error during application: </t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4705,87 +4705,67 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:03.584167+00:00</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:33:06.925683+00:00</t>
+          <t>2026-10-29T15:57:30.736929+00:00</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-29T14:33:03.491808+00:00</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:33:06.712055+00:00</t>
+          <t>2026-10-29T15:57:30.641685+00:00</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4795,67 +4775,92 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.474877+00:00</t>
+          <t>2026-10-29T15:57:30.320583+00:00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:57:30.326118+00:00</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.425587+00:00</t>
+          <t>2026-10-29T15:42:54.287293+00:00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:42:58.032370+00:00</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4865,33 +4870,28 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.260452+00:00</t>
+          <t>2026-10-29T15:42:54.177389+00:00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-10-29T14:32:58.272949+00:00</t>
+          <t>2026-10-29T15:42:58.180926+00:00</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:56.380448+00:00</t>
+          <t>2026-10-29T14:38:27.443320+00:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-10-29T14:27:00.101381+00:00</t>
+          <t>2026-10-29T14:38:31.782682+00:00</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4936,7 +4936,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4960,12 +4960,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:56.297032+00:00</t>
+          <t>2026-10-29T14:38:27.356218+00:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:59.916918+00:00</t>
+          <t>2026-10-29T14:38:31.839164+00:00</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4981,7 +4981,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.411181+00:00</t>
+          <t>2026-10-29T14:38:22.075427+00:00</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5016,7 +5016,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.360006+00:00</t>
+          <t>2026-10-29T14:38:22.021258+00:00</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5051,7 +5051,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.196399+00:00</t>
+          <t>2026-10-29T14:38:21.847719+00:00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-10-29T14:26:51.202839+00:00</t>
+          <t>2026-10-29T14:38:21.862410+00:00</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5101,7 +5101,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -5125,12 +5125,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:32.778042+00:00</t>
+          <t>2026-10-29T14:33:03.584167+00:00</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:36.309759+00:00</t>
+          <t>2026-10-29T14:33:06.925683+00:00</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5146,7 +5146,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:32.702160+00:00</t>
+          <t>2026-10-29T14:33:03.491808+00:00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-10-29T14:14:36.201815+00:00</t>
+          <t>2026-10-29T14:33:06.712055+00:00</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5191,21 +5191,21 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5215,87 +5215,67 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:16.189456+00:00</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:12:19.790801+00:00</t>
+          <t>2026-10-29T14:32:58.474877+00:00</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:16.112025+00:00</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2026-10-29T14:12:19.994696+00:00</t>
+          <t>2026-10-29T14:32:58.425587+00:00</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5305,67 +5285,92 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.875174+00:00</t>
+          <t>2026-10-29T14:32:58.260452+00:00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:32:58.272949+00:00</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.820231+00:00</t>
+          <t>2026-10-29T14:26:56.380448+00:00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:27:00.101381+00:00</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5375,47 +5380,42 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.636542+00:00</t>
+          <t>2026-10-29T14:26:56.297032+00:00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-10-29T14:12:11.641061+00:00</t>
+          <t>2026-10-29T14:26:59.916918+00:00</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5425,87 +5425,67 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:57.519802+00:00</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2026-10-29T13:32:01.165745+00:00</t>
+          <t>2026-10-29T14:26:51.411181+00:00</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:57.442785+00:00</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2026-10-29T13:32:01.304468+00:00</t>
+          <t>2026-10-29T14:26:51.360006+00:00</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5515,67 +5495,92 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.587292+00:00</t>
+          <t>2026-10-29T14:26:51.196399+00:00</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:26:51.202839+00:00</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.538735+00:00</t>
+          <t>2026-10-29T14:14:32.778042+00:00</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:14:36.309759+00:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5585,33 +5590,28 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.383044+00:00</t>
+          <t>2026-10-29T14:14:32.702160+00:00</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-10-29T13:31:52.386957+00:00</t>
+          <t>2026-10-29T14:14:36.201815+00:00</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Smoke test OK</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:02.362074+00:00</t>
+          <t>2026-10-29T14:12:16.189456+00:00</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:08.021605+00:00</t>
+          <t>2026-10-29T14:12:19.790801+00:00</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5656,7 +5656,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -5680,12 +5680,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:02.284388+00:00</t>
+          <t>2026-10-29T14:12:16.112025+00:00</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-10-29T13:01:08.052421+00:00</t>
+          <t>2026-10-29T14:12:19.994696+00:00</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5701,7 +5701,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.427420+00:00</t>
+          <t>2026-10-29T14:12:11.875174+00:00</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5736,7 +5736,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.330669+00:00</t>
+          <t>2026-10-29T14:12:11.820231+00:00</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.020667+00:00</t>
+          <t>2026-10-29T14:12:11.636542+00:00</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-10-29T13:00:30.032548+00:00</t>
+          <t>2026-10-29T14:12:11.641061+00:00</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5821,7 +5821,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:43.958358+00:00</t>
+          <t>2026-10-29T13:31:57.519802+00:00</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:47.842477+00:00</t>
+          <t>2026-10-29T13:32:01.165745+00:00</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5866,7 +5866,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -5890,12 +5890,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:43.875277+00:00</t>
+          <t>2026-10-29T13:31:57.442785+00:00</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:47.826697+00:00</t>
+          <t>2026-10-29T13:32:01.304468+00:00</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5911,7 +5911,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.679674+00:00</t>
+          <t>2026-10-29T13:31:52.587292+00:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5946,7 +5946,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.612816+00:00</t>
+          <t>2026-10-29T13:31:52.538735+00:00</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5981,7 +5981,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -6005,12 +6005,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.402785+00:00</t>
+          <t>2026-10-29T13:31:52.383044+00:00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:38.409018+00:00</t>
+          <t>2026-10-29T13:31:52.386957+00:00</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6031,66 +6031,66 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CredHive</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI Systems)</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/software-engineer-intern-at-credhive-4483104685?trk=public_jobs_topcard-title</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-29T07:40:04.055848+00:00</t>
+          <t>2026-10-29T13:01:02.362074+00:00</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-10-29T07:40:08.038425+00:00</t>
+          <t>2026-10-29T13:01:08.021605+00:00</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Needs manual action</t>
+          <t>Aborted by user</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6100,42 +6100,52 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.906851+00:00</t>
+          <t>2026-10-29T13:01:02.284388+00:00</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:01:08.052421+00:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.830142+00:00</t>
+          <t>2026-10-29T13:00:30.427420+00:00</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6146,57 +6156,42 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>smoke-001</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TestCorp</t>
+          <t>DemoCorp</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>http://localhost:5000/test_form.html</t>
+          <t>http://localhost/test</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:46.609768+00:00</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>2026-10-29T07:35:46.623780+00:00</t>
+          <t>2026-10-29T13:00:30.330669+00:00</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Submitted successfully</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Confirmed in test</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Smoke test OK</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -6220,42 +6215,47 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:04.749633+00:00</t>
+          <t>2026-10-29T13:00:30.020667+00:00</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:08.318789+00:00</t>
+          <t>2026-10-29T13:00:30.032548+00:00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Aborted by user</t>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Application aborted by user. No submission was made.</t>
+          <t>Smoke test OK</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>api-test-99</t>
+          <t>smoke-001</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>API Test Corp</t>
+          <t>TestCorp</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6265,12 +6265,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:04.683354+00:00</t>
+          <t>2026-10-29T12:35:43.958358+00:00</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-10-29T07:35:08.243543+00:00</t>
+          <t>2026-10-29T12:35:47.842477+00:00</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6286,21 +6286,21 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>api-test-99</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>API Test Corp</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6310,42 +6310,52 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:00.218486+00:00</t>
+          <t>2026-10-29T12:35:43.875277+00:00</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:47.826697+00:00</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DemoCorp</t>
+          <t>Demo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>http://localhost/test</t>
+          <t>http://localhost:5000/test_form.html</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:00.030655+00:00</t>
+          <t>2026-10-29T12:35:38.679674+00:00</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6356,49 +6366,459 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
+        <v>11</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.612816+00:00</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>10</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.402785+00:00</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:35:38.409018+00:00</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>9</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CredHive</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (AI Systems)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/software-engineer-intern-at-credhive-4483104685?trk=public_jobs_topcard-title</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:40:04.055848+00:00</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:40:08.038425+00:00</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Needs manual action</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Automated form filling is not available for this site. Please complete the application manually in the browser window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>8</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.906851+00:00</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>7</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.830142+00:00</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>6</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.609768+00:00</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:46.623780+00:00</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Submitted successfully</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Confirmed in test</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Smoke test OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>5</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>smoke-001</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>TestCorp</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:04.749633+00:00</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:08.318789+00:00</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>api-test-99</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>API Test Corp</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Test Engineer</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:04.683354+00:00</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:35:08.243543+00:00</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Aborted by user</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Application aborted by user. No submission was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>3</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:24:00.218486+00:00</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DemoCorp</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>http://localhost/test</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-10-29T07:24:00.030655+00:00</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
         <v>1</v>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>smoke-001</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>TestCorp</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>http://localhost:5000/test_form.html</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>http://localhost:5000/test_form.html</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
         <is>
           <t>2026-10-29T07:23:59.720577+00:00</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>2026-10-29T07:23:59.730420+00:00</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>Submitted successfully</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>Confirmed in test</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="K153" t="inlineStr">
         <is>
           <t>Smoke test OK</t>
         </is>
